--- a/analises/vinhos/tanyno-tintos-espanha-2026-10-13.xlsx
+++ b/analises/vinhos/tanyno-tintos-espanha-2026-10-13.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8268"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Tintos Espanha" state="visible" r:id="rId4"/>
+    <sheet name="Tintos Espanha" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="51">
   <si>
     <t>Linha</t>
   </si>
@@ -67,15 +70,6 @@
     <t>Priorat</t>
   </si>
   <si>
-    <t>Dolç de l'Obac</t>
-  </si>
-  <si>
-    <t>Tinto doce (sobremesa)</t>
-  </si>
-  <si>
-    <t>Dolç de l'Obac 500ml</t>
-  </si>
-  <si>
     <t>Miserere</t>
   </si>
   <si>
@@ -97,13 +91,7 @@
     <t>La Quinta Cruz</t>
   </si>
   <si>
-    <t>Gran Reserva</t>
-  </si>
-  <si>
     <t>La Loma</t>
-  </si>
-  <si>
-    <t>Reserva</t>
   </si>
   <si>
     <t>Viñas Jóvenes</t>
@@ -186,27 +174,32 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-    </font>
-    <font>
-      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -260,7 +253,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -270,44 +263,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -337,12 +330,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -381,208 +374,149 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
@@ -594,7 +528,7 @@
     <col min="9" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -623,7 +557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -646,14 +580,14 @@
         <v>98.77</v>
       </c>
       <c r="H2" s="2">
-        <f>ROUNDUP(ROUND(G2*1.21,2)+5,0)</f>
+        <f t="shared" ref="H2:H28" si="0">ROUNDUP(ROUND(G2*1.21,2)+5,0)</f>
         <v>125</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -676,14 +610,14 @@
         <v>150.75</v>
       </c>
       <c r="H3" s="2">
-        <f>ROUNDUP(ROUND(G3*1.21,2)+5,0)</f>
+        <f t="shared" si="0"/>
         <v>188</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -706,14 +640,14 @@
         <v>589.65</v>
       </c>
       <c r="H4" s="2">
-        <f>ROUNDUP(ROUND(G4*1.21,2)+5,0)</f>
+        <f t="shared" si="0"/>
         <v>719</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -736,14 +670,14 @@
         <v>1080.79</v>
       </c>
       <c r="H5" s="2">
-        <f>ROUNDUP(ROUND(G5*1.21,2)+5,0)</f>
+        <f t="shared" si="0"/>
         <v>1313</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -754,26 +688,26 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1">
-        <v>811.66</v>
+        <v>954.12</v>
       </c>
       <c r="H6" s="2">
-        <f>ROUNDUP(ROUND(G6*1.21,2)+5,0)</f>
-        <v>988</v>
+        <f t="shared" si="0"/>
+        <v>1160</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -781,119 +715,119 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>173</v>
       </c>
       <c r="G7" s="1">
-        <v>658.34</v>
+        <v>266.04000000000002</v>
       </c>
       <c r="H7" s="2">
-        <f>ROUNDUP(ROUND(G7*1.21,2)+5,0)</f>
-        <v>802</v>
+        <f t="shared" si="0"/>
+        <v>327</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
       <c r="D8">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <v>543.59</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>663</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="1">
-        <v>954.12</v>
-      </c>
-      <c r="H8" s="2">
-        <f>ROUNDUP(ROUND(G8*1.21,2)+5,0)</f>
-        <v>1160</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
       <c r="D9">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="G9" s="1">
-        <v>812.19</v>
+        <v>239.18</v>
       </c>
       <c r="H9" s="2">
-        <f>ROUNDUP(ROUND(G9*1.21,2)+5,0)</f>
-        <v>988</v>
+        <f t="shared" si="0"/>
+        <v>295</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>173</v>
+        <v>25</v>
       </c>
       <c r="G10" s="1">
-        <v>266.04</v>
+        <v>350.19</v>
       </c>
       <c r="H10" s="2">
-        <f>ROUNDUP(ROUND(G10*1.21,2)+5,0)</f>
-        <v>327</v>
+        <f t="shared" si="0"/>
+        <v>429</v>
       </c>
       <c r="I10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -901,29 +835,29 @@
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1">
-        <v>543.59</v>
+        <v>529.26</v>
       </c>
       <c r="H11" s="2">
-        <f>ROUNDUP(ROUND(G11*1.21,2)+5,0)</f>
-        <v>663</v>
+        <f t="shared" si="0"/>
+        <v>646</v>
       </c>
       <c r="I11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -931,37 +865,37 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
       <c r="F12">
-        <v>152</v>
+        <v>239</v>
       </c>
       <c r="G12" s="1">
-        <v>239.18</v>
+        <v>153.22</v>
       </c>
       <c r="H12" s="2">
-        <f>ROUNDUP(ROUND(G12*1.21,2)+5,0)</f>
-        <v>295</v>
+        <f t="shared" si="0"/>
+        <v>191</v>
       </c>
       <c r="I12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
       </c>
       <c r="D13">
         <v>2022</v>
@@ -970,55 +904,55 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <v>25</v>
+        <v>504</v>
       </c>
       <c r="G13" s="1">
-        <v>350.19</v>
+        <v>153.22</v>
       </c>
       <c r="H13" s="2">
-        <f>ROUNDUP(ROUND(G13*1.21,2)+5,0)</f>
-        <v>429</v>
+        <f t="shared" si="0"/>
+        <v>191</v>
       </c>
       <c r="I13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1">
-        <v>439.74</v>
+        <v>260.67</v>
       </c>
       <c r="H14" s="2">
-        <f>ROUNDUP(ROUND(G14*1.21,2)+5,0)</f>
-        <v>538</v>
+        <f t="shared" si="0"/>
+        <v>321</v>
       </c>
       <c r="I14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
@@ -1027,570 +961,419 @@
         <v>2022</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1">
-        <v>529.26</v>
+        <v>358.53</v>
       </c>
       <c r="H15" s="2">
-        <f>ROUNDUP(ROUND(G15*1.21,2)+5,0)</f>
-        <v>646</v>
+        <f t="shared" si="0"/>
+        <v>439</v>
       </c>
       <c r="I15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>2023</v>
+      </c>
+      <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="D16">
-        <v>2019</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
       <c r="F16">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G16" s="1">
-        <v>314.39</v>
+        <v>280.5</v>
       </c>
       <c r="H16" s="2">
-        <f>ROUNDUP(ROUND(G16*1.21,2)+5,0)</f>
-        <v>386</v>
+        <f t="shared" si="0"/>
+        <v>345</v>
       </c>
       <c r="I16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>239</v>
+        <v>117</v>
       </c>
       <c r="G17" s="1">
-        <v>153.22</v>
+        <v>129.74</v>
       </c>
       <c r="H17" s="2">
-        <f>ROUNDUP(ROUND(G17*1.21,2)+5,0)</f>
-        <v>191</v>
+        <f t="shared" si="0"/>
+        <v>162</v>
       </c>
       <c r="I17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>2022</v>
       </c>
       <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>31</v>
+      </c>
+      <c r="G18" s="1">
+        <v>358.53</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="0"/>
+        <v>439</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19">
+        <v>2022</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19">
+        <v>84</v>
+      </c>
+      <c r="G19" s="1">
+        <v>272.87</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="0"/>
+        <v>336</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20">
+        <v>2020</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20">
+        <v>11</v>
+      </c>
+      <c r="G20" s="1">
+        <v>239.17</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="0"/>
+        <v>295</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21">
+        <v>2019</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21">
         <v>12</v>
       </c>
-      <c r="F18">
-        <v>504</v>
-      </c>
-      <c r="G18" s="1">
-        <v>153.22</v>
-      </c>
-      <c r="H18" s="2">
-        <f>ROUNDUP(ROUND(G18*1.21,2)+5,0)</f>
-        <v>191</v>
-      </c>
-      <c r="I18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19">
-        <v>2020</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19">
-        <v>19</v>
-      </c>
-      <c r="G19" s="1">
-        <v>260.67</v>
-      </c>
-      <c r="H19" s="2">
-        <f>ROUNDUP(ROUND(G19*1.21,2)+5,0)</f>
-        <v>321</v>
-      </c>
-      <c r="I19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20">
-        <v>2022</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="G21" s="1">
+        <v>983.22</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="0"/>
+        <v>1195</v>
+      </c>
+      <c r="I21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>35</v>
       </c>
-      <c r="F20">
-        <v>26</v>
-      </c>
-      <c r="G20" s="1">
-        <v>358.53</v>
-      </c>
-      <c r="H20" s="2">
-        <f>ROUNDUP(ROUND(G20*1.21,2)+5,0)</f>
-        <v>439</v>
-      </c>
-      <c r="I20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
         <v>36</v>
       </c>
-      <c r="D21">
-        <v>2023</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22">
+        <v>2017</v>
+      </c>
+      <c r="E22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1">
+        <v>485.69</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="0"/>
+        <v>593</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>35</v>
       </c>
-      <c r="F21">
-        <v>14</v>
-      </c>
-      <c r="G21" s="1">
-        <v>280.5</v>
-      </c>
-      <c r="H21" s="2">
-        <f>ROUNDUP(ROUND(G21*1.21,2)+5,0)</f>
-        <v>345</v>
-      </c>
-      <c r="I21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22">
-        <v>2022</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22">
-        <v>117</v>
-      </c>
-      <c r="G22" s="1">
-        <v>129.74</v>
-      </c>
-      <c r="H22" s="2">
-        <f>ROUNDUP(ROUND(G22*1.21,2)+5,0)</f>
-        <v>162</v>
-      </c>
-      <c r="I22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D23">
         <v>2022</v>
       </c>
       <c r="E23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23">
+        <v>69</v>
+      </c>
+      <c r="G23" s="1">
+        <v>375.3</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>35</v>
       </c>
-      <c r="F23">
-        <v>31</v>
-      </c>
-      <c r="G23" s="1">
-        <v>358.53</v>
-      </c>
-      <c r="H23" s="2">
-        <f>ROUNDUP(ROUND(G23*1.21,2)+5,0)</f>
-        <v>439</v>
-      </c>
-      <c r="I23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D24">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>23</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2120.4</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="0"/>
+        <v>2571</v>
+      </c>
+      <c r="I24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>35</v>
       </c>
-      <c r="F24">
-        <v>84</v>
-      </c>
-      <c r="G24" s="1">
-        <v>272.87</v>
-      </c>
-      <c r="H24" s="2">
-        <f>ROUNDUP(ROUND(G24*1.21,2)+5,0)</f>
-        <v>336</v>
-      </c>
-      <c r="I24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D25">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>428</v>
       </c>
       <c r="G25" s="1">
-        <v>239.17</v>
+        <v>196.76</v>
       </c>
       <c r="H25" s="2">
-        <f>ROUNDUP(ROUND(G25*1.21,2)+5,0)</f>
-        <v>295</v>
+        <f t="shared" si="0"/>
+        <v>244</v>
       </c>
       <c r="I25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D26">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E26" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="G26" s="1">
-        <v>983.22</v>
+        <v>494.72</v>
       </c>
       <c r="H26" s="2">
-        <f>ROUNDUP(ROUND(G26*1.21,2)+5,0)</f>
-        <v>1195</v>
+        <f t="shared" si="0"/>
+        <v>604</v>
       </c>
       <c r="I26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27">
+        <v>2021</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27">
+        <v>24</v>
+      </c>
+      <c r="G27" s="1">
+        <v>668.44</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="0"/>
+        <v>814</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
         <v>45</v>
       </c>
-      <c r="D27">
-        <v>2017</v>
-      </c>
-      <c r="E27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27">
-        <v>15</v>
-      </c>
-      <c r="G27" s="1">
-        <v>485.69</v>
-      </c>
-      <c r="H27" s="2">
-        <f>ROUNDUP(ROUND(G27*1.21,2)+5,0)</f>
-        <v>593</v>
-      </c>
-      <c r="I27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D28">
         <v>2022</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F28">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="G28" s="1">
-        <v>375.3</v>
+        <v>107.11</v>
       </c>
       <c r="H28" s="2">
-        <f>ROUNDUP(ROUND(G28*1.21,2)+5,0)</f>
-        <v>460</v>
+        <f t="shared" si="0"/>
+        <v>135</v>
       </c>
       <c r="I28" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29">
-        <v>2019</v>
-      </c>
-      <c r="E29" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29">
-        <v>23</v>
-      </c>
-      <c r="G29" s="1">
-        <v>2120.4</v>
-      </c>
-      <c r="H29" s="2">
-        <f>ROUNDUP(ROUND(G29*1.21,2)+5,0)</f>
-        <v>2571</v>
-      </c>
-      <c r="I29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30">
-        <v>2021</v>
-      </c>
-      <c r="E30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30">
-        <v>428</v>
-      </c>
-      <c r="G30" s="1">
-        <v>196.76</v>
-      </c>
-      <c r="H30" s="2">
-        <f>ROUNDUP(ROUND(G30*1.21,2)+5,0)</f>
-        <v>244</v>
-      </c>
-      <c r="I30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31">
-        <v>2021</v>
-      </c>
-      <c r="E31" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31">
-        <v>64</v>
-      </c>
-      <c r="G31" s="1">
-        <v>494.72</v>
-      </c>
-      <c r="H31" s="2">
-        <f>ROUNDUP(ROUND(G31*1.21,2)+5,0)</f>
-        <v>604</v>
-      </c>
-      <c r="I31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32">
-        <v>2021</v>
-      </c>
-      <c r="E32" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32">
-        <v>24</v>
-      </c>
-      <c r="G32" s="1">
-        <v>668.44</v>
-      </c>
-      <c r="H32" s="2">
-        <f>ROUNDUP(ROUND(G32*1.21,2)+5,0)</f>
-        <v>814</v>
-      </c>
-      <c r="I32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33">
-        <v>2022</v>
-      </c>
-      <c r="E33" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33">
-        <v>128</v>
-      </c>
-      <c r="G33" s="1">
-        <v>107.11</v>
-      </c>
-      <c r="H33" s="2">
-        <f>ROUNDUP(ROUND(G33*1.21,2)+5,0)</f>
-        <v>135</v>
-      </c>
-      <c r="I33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>55</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>